--- a/data/external/complete_classification_41.xlsx
+++ b/data/external/complete_classification_41.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\PycharmProjects\youtube_data\data\external\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7176A01-5556-40E6-BC85-ED8DBAA6722C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09E6C10-3C56-45F6-91E3-039B0F7216B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>video_id</t>
   </si>
@@ -88,6 +88,60 @@
   </si>
   <si>
     <t>de45kIKK3rk</t>
+  </si>
+  <si>
+    <t>XrBc-gCs_pU</t>
+  </si>
+  <si>
+    <t>oo_3bfwr51w</t>
+  </si>
+  <si>
+    <t>Z-ZD0y4HieY</t>
+  </si>
+  <si>
+    <t>BjIpufQd7sw</t>
+  </si>
+  <si>
+    <t>w1MVzaUy9dw</t>
+  </si>
+  <si>
+    <t>K6aIHAHsAMU</t>
+  </si>
+  <si>
+    <t>nocck3tNk_8</t>
+  </si>
+  <si>
+    <t>fwDDIOG6LTk</t>
+  </si>
+  <si>
+    <t>nvkJV3L_wYo</t>
+  </si>
+  <si>
+    <t>Z_tVBgPysGQ</t>
+  </si>
+  <si>
+    <t>lIHZjD7Jw0U</t>
+  </si>
+  <si>
+    <t>JcrtCo-US1c</t>
+  </si>
+  <si>
+    <t>PRPW3uL78rk</t>
+  </si>
+  <si>
+    <t>IibpPaE1d-o</t>
+  </si>
+  <si>
+    <t>x68t3aDdZDo</t>
+  </si>
+  <si>
+    <t>pR0usp1PCO4</t>
+  </si>
+  <si>
+    <t>ASr8tOLtQP4</t>
+  </si>
+  <si>
+    <t>bwctuqdk-XI</t>
   </si>
 </sst>
 </file>
@@ -406,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -682,6 +736,330 @@
         <v>7.5</v>
       </c>
     </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>-1</v>
+      </c>
+      <c r="E16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>-1</v>
+      </c>
+      <c r="E17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>9</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>-1</v>
+      </c>
+      <c r="E19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>4.5</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>8</v>
+      </c>
+      <c r="E24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>9</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>9</v>
+      </c>
+      <c r="E26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>8</v>
+      </c>
+      <c r="E27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>9.5</v>
+      </c>
+      <c r="E30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>-1</v>
+      </c>
+      <c r="E31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/external/complete_classification_41.xlsx
+++ b/data/external/complete_classification_41.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\PycharmProjects\youtube_data\data\external\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09E6C10-3C56-45F6-91E3-039B0F7216B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81ABE46B-C562-4CE5-9825-18558C9B8818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>video_id</t>
   </si>
@@ -142,6 +142,51 @@
   </si>
   <si>
     <t>bwctuqdk-XI</t>
+  </si>
+  <si>
+    <t>ZQ6inX60tqQ</t>
+  </si>
+  <si>
+    <t>_T9axTIB6B0</t>
+  </si>
+  <si>
+    <t>0jhTRcfvaTA</t>
+  </si>
+  <si>
+    <t>ppQPM8Ea-94</t>
+  </si>
+  <si>
+    <t>gD7_n7ciPvc</t>
+  </si>
+  <si>
+    <t>9Lq2MaTxaXA</t>
+  </si>
+  <si>
+    <t>eCy_eEm8jgA</t>
+  </si>
+  <si>
+    <t>UCKi8pj2bEA</t>
+  </si>
+  <si>
+    <t>1mv8GVl937s</t>
+  </si>
+  <si>
+    <t>DjaRa1bn7iA</t>
+  </si>
+  <si>
+    <t>oUTz3-T9Ofw</t>
+  </si>
+  <si>
+    <t>CTIcShw63cE</t>
+  </si>
+  <si>
+    <t>VPAvRQHTAcE</t>
+  </si>
+  <si>
+    <t>mTMk4g0-loA</t>
+  </si>
+  <si>
+    <t>8Y4QyMhMvls</t>
   </si>
 </sst>
 </file>
@@ -460,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -598,6 +643,18 @@
       <c r="A8" t="s">
         <v>13</v>
       </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
@@ -1058,6 +1115,261 @@
       </c>
       <c r="E33">
         <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>5</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>-1</v>
+      </c>
+      <c r="E38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>-1</v>
+      </c>
+      <c r="E40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>-1</v>
+      </c>
+      <c r="E44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>-1</v>
+      </c>
+      <c r="E46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>-1</v>
+      </c>
+      <c r="E47">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>-1</v>
+      </c>
+      <c r="E48">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
